--- a/NCU_Club_Starring_History.xlsx
+++ b/NCU_Club_Starring_History.xlsx
@@ -3,11 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="42630" yWindow="1575" windowWidth="31845" windowHeight="18645" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Starring Audit Trail" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="International Exemptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Board_Dispensations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -503,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -543,17 +544,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Men's</t>
+          <t>Women's</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Waringstown</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mark Adair</t>
+          <t>Cara Murray</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -563,7 +564,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-18 20:14:43</t>
+          <t>2026-09-18 20:20:41</t>
         </is>
       </c>
     </row>
@@ -575,22 +576,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Amigos Belfast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ben Calitz</t>
+          <t>[None]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Active Exemption</t>
+          <t>No Exemptions</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-18 20:14:43</t>
+          <t>2026-09-22 10:45:22</t>
         </is>
       </c>
     </row>
@@ -602,374 +603,171 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Lisburn</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[None]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>No Exemptions</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:01:51</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="111" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Club Name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Allowed Lower Tier</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Dispensation Reason</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Effective Season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Simon King</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Larne</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unstarred</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cannot play Saturdays - Sunday availability only</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Zayyan Malik</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Waringstown</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2nd XI</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Still not good enough to be starred for 1st XI</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Steve Stolk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Waringstown</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[None]</t>
+          <t>Unstarred</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:15:29</t>
-        </is>
+          <t>No longer their overseas pro</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2027</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Men's</t>
+          <t>Nikolai Smith</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BISC</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[None]</t>
+          <t>2nd XI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:17:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Men's</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Amigos Belfast</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:18:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Men's</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Arches</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:18:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Men's</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ardent Blues</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:18:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Women's</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bangor</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:19:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Women's</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CSNI</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:19:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Women's</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Holywood</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Women's</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Instonians</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Women's</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Lisburn</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:20:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Women's</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Muckamore</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:20:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Women's</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>North Down</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:20:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Women's</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Waringstown</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Cara Murray</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Active Exemption</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-09-18 20:20:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Men's</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Bangor</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[None]</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>No Exemptions</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-09-19 15:13:13</t>
-        </is>
+          <t>Must be starred for at least 2nd XI as he has played the majority of his recent cricket in the Premier League</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2027</v>
       </c>
     </row>
   </sheetData>
